--- a/human_resources_forms/049_fitness_reimbursement_form--human_resources_forms.xlsx
+++ b/human_resources_forms/049_fitness_reimbursement_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'terminated',_'label':_'terminated'}</t>
+          <t>terminated</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'terminated', 'label': 'Terminated'}</t>
+          <t>Terminated</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'full-time',_'label':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'full-time', 'label': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'part-time',_'label':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'part-time', 'label': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'contract',_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'contract', 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'gym_member',_'label':_'gym_member'}</t>
+          <t>gym_member</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'gym_member', 'label': 'Gym Member'}</t>
+          <t>Gym Member</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'class_member',_'label':_'class_member'}</t>
+          <t>class_member</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'class_member', 'label': 'Class Member'}</t>
+          <t>Class Member</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'membership',_'label':_'membership'}</t>
+          <t>membership</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'membership', 'label': 'Membership'}</t>
+          <t>Membership</t>
         </is>
       </c>
     </row>
